--- a/Watchlist .xlsx
+++ b/Watchlist .xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{493808E5-B68B-42A3-9C80-6FFB625C3D0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5653B5D0-E691-4788-8025-A1E4EB75A9CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="2340" windowWidth="38175" windowHeight="15240" activeTab="1" xr2:uid="{17ABFCAF-F8B8-4F77-A601-F3F3D02F1763}"/>
+    <workbookView xWindow="225" yWindow="2340" windowWidth="38175" windowHeight="15240" xr2:uid="{17ABFCAF-F8B8-4F77-A601-F3F3D02F1763}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="100">
   <si>
     <t>Watchlist</t>
   </si>
@@ -368,6 +368,12 @@
   <si>
     <t xml:space="preserve">Sports </t>
   </si>
+  <si>
+    <t>QXO</t>
+  </si>
+  <si>
+    <t>NE</t>
+  </si>
 </sst>
 </file>
 
@@ -377,13 +383,19 @@
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\)"/>
     <numFmt numFmtId="165" formatCode="#,##0.0;\(#,##0.0\)"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -528,104 +540,105 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="16" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="16" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="16" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="17" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="16" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="16" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="17" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="16" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8" customBuiltin="1"/>
@@ -2220,6 +2233,12 @@
       <c r="B14" s="7" t="s">
         <v>95</v>
       </c>
+      <c r="C14" s="48" t="s">
+        <v>95</v>
+      </c>
+      <c r="D14" s="48" t="s">
+        <v>99</v>
+      </c>
       <c r="F14" s="12"/>
       <c r="G14" s="12"/>
       <c r="H14" s="12"/>
@@ -2230,6 +2249,15 @@
       <c r="A15" s="11">
         <f t="shared" si="2"/>
         <v>11</v>
+      </c>
+      <c r="B15" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="C15" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="D15" s="48" t="s">
+        <v>24</v>
       </c>
       <c r="F15" s="12"/>
       <c r="G15" s="12"/>

--- a/Watchlist .xlsx
+++ b/Watchlist .xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5653B5D0-E691-4788-8025-A1E4EB75A9CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50DE31E4-C50F-413D-B976-E1A5EEF90F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="2340" windowWidth="38175" windowHeight="15240" xr2:uid="{17ABFCAF-F8B8-4F77-A601-F3F3D02F1763}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{17ABFCAF-F8B8-4F77-A601-F3F3D02F1763}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
     <sheet name="Portfolio" sheetId="3" r:id="rId2"/>
-    <sheet name="FX" sheetId="2" r:id="rId3"/>
+    <sheet name="IPO" sheetId="4" r:id="rId3"/>
+    <sheet name="FX" sheetId="2" r:id="rId4"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId4"/>
     <externalReference r:id="rId5"/>
     <externalReference r:id="rId6"/>
     <externalReference r:id="rId7"/>
@@ -33,6 +33,7 @@
     <externalReference r:id="rId16"/>
     <externalReference r:id="rId17"/>
     <externalReference r:id="rId18"/>
+    <externalReference r:id="rId19"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -73,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="103">
   <si>
     <t>Watchlist</t>
   </si>
@@ -374,6 +375,15 @@
   <si>
     <t>NE</t>
   </si>
+  <si>
+    <t>IPO-Date</t>
+  </si>
+  <si>
+    <t>Oura</t>
+  </si>
+  <si>
+    <t>Dangote Refinery</t>
+  </si>
 </sst>
 </file>
 
@@ -383,13 +393,19 @@
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\)"/>
     <numFmt numFmtId="165" formatCode="#,##0.0;\(#,##0.0\)"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -540,105 +556,110 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="16" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="16" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="16" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="16" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="17" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="16" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="17" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="16" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8" customBuiltin="1"/>
@@ -659,6 +680,48 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Quarters"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>66.3</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>1333.3824387</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>315.70799999999997</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>449.74</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -710,253 +773,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-      <sheetName val="Ratios"/>
-      <sheetName val="CoC"/>
-      <sheetName val="DCF"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>59.96</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>9165.7399503199995</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>752.101</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>1994.925</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>111</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>1937593.7999999998</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>374857</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="J7">
-            <v>75503</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>87.92</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>5978.0039939199996</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>180.76900000000001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>399.72299999999996</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>160.9</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>213851.54640000002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>13765.710999999999</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>113.5</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>50394</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>2919</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>6746</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>50.7</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>27269.090670900005</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>1068</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>30199</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1008,7 +825,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1058,7 +875,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1098,7 +915,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1149,7 +966,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1209,93 +1026,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-      <sheetName val="Ratios"/>
-      <sheetName val="DCF"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>110.86</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>12021.43191302</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>1514.729</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Quarters"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>66.3</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>1333.3824387</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>315.70799999999997</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>449.74</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1326,6 +1057,296 @@
         <row r="6">
           <cell r="I6">
             <v>3534.607</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+      <sheetName val="Ratios"/>
+      <sheetName val="DCF"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>99.65</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>10522.448477600001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>189.73699999999999</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+      <sheetName val="Ratios"/>
+      <sheetName val="CoC"/>
+      <sheetName val="DCF"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>59.96</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>9165.7399503199995</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>752.101</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>1994.925</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>111</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>1937593.7999999998</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>374857</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="J7">
+            <v>75503</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>87.92</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>5978.0039939199996</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>180.76900000000001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>399.72299999999996</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>160.9</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>213851.54640000002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>13765.710999999999</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>113.5</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>50394</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>2919</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>6746</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>50.7</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>27269.090670900005</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>1068</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>30199</v>
           </cell>
         </row>
       </sheetData>
@@ -1754,15 +1775,15 @@
         <v>16</v>
       </c>
       <c r="E5" s="9">
-        <f>+[8]Main!$J$2</f>
+        <f>+[1]Main!$J$2</f>
         <v>66.3</v>
       </c>
       <c r="F5" s="12">
-        <f>+[8]Main!$J$4*FX!C2</f>
+        <f>+[1]Main!$J$4*FX!C2</f>
         <v>1560.0574532789999</v>
       </c>
       <c r="G5" s="12">
-        <f>(+[8]Main!$J$6-[8]Main!$J$5)*FX!C2</f>
+        <f>(+[1]Main!$J$6-[1]Main!$J$5)*FX!C2</f>
         <v>156.81744000000003</v>
       </c>
       <c r="H5" s="12">
@@ -1807,15 +1828,15 @@
         <v>24</v>
       </c>
       <c r="E6" s="9">
-        <f>+[9]Main!$I$2</f>
+        <f>+[2]Main!$I$2</f>
         <v>5.29</v>
       </c>
       <c r="F6" s="12">
-        <f>+[9]Main!$I$4</f>
+        <f>+[2]Main!$I$4</f>
         <v>8946.4358964800012</v>
       </c>
       <c r="G6" s="12">
-        <f>+[9]Main!$I$6-[9]Main!$I$5</f>
+        <f>+[2]Main!$I$6-[2]Main!$I$5</f>
         <v>874.84900000000016</v>
       </c>
       <c r="H6" s="12">
@@ -1863,20 +1884,20 @@
         <v>29</v>
       </c>
       <c r="E7" s="9">
-        <f>+[7]Main!$I$2</f>
-        <v>110.86</v>
+        <f>+[3]Main!$I$2</f>
+        <v>99.65</v>
       </c>
       <c r="F7" s="12">
-        <f>+[7]Main!$I$4</f>
-        <v>12021.43191302</v>
+        <f>+[3]Main!$I$4</f>
+        <v>10522.448477600001</v>
       </c>
       <c r="G7" s="12">
-        <f>+[7]Main!$I$6-[7]Main!$I$5</f>
-        <v>-1514.729</v>
+        <f>+[3]Main!$I$6-[3]Main!$I$5</f>
+        <v>-189.73699999999999</v>
       </c>
       <c r="H7" s="12">
         <f t="shared" si="0"/>
-        <v>10506.702913020001</v>
+        <v>10332.711477600002</v>
       </c>
       <c r="I7" s="17" t="s">
         <v>18</v>
@@ -1892,7 +1913,7 @@
       </c>
       <c r="M7" s="18">
         <f t="shared" si="1"/>
-        <v>-0.44114533447597926</v>
+        <v>-0.49765589554872203</v>
       </c>
       <c r="O7" s="10" t="s">
         <v>35</v>
@@ -1916,15 +1937,15 @@
         <v>24</v>
       </c>
       <c r="E8" s="9">
-        <f>+[10]Main!$H$2</f>
+        <f>+[4]Main!$H$2</f>
         <v>59.96</v>
       </c>
       <c r="F8" s="12">
-        <f>+[10]Main!$H$4</f>
+        <f>+[4]Main!$H$4</f>
         <v>9165.7399503199995</v>
       </c>
       <c r="G8" s="12">
-        <f>+[10]Main!$H$6-[10]Main!$H$5</f>
+        <f>+[4]Main!$H$6-[4]Main!$H$5</f>
         <v>1242.8240000000001</v>
       </c>
       <c r="H8" s="12">
@@ -1969,15 +1990,15 @@
         <v>39</v>
       </c>
       <c r="E9" s="9">
-        <f>+[11]Main!$J$2</f>
+        <f>+[5]Main!$J$2</f>
         <v>111</v>
       </c>
       <c r="F9" s="12">
-        <f>+[11]Main!$J$5*FX!C3</f>
+        <f>+[5]Main!$J$5*FX!C3</f>
         <v>271263.13199999998</v>
       </c>
       <c r="G9" s="12">
-        <f>+([11]Main!$J$7-[11]Main!$J$6)*FX!C3</f>
+        <f>+([5]Main!$J$7-[5]Main!$J$6)*FX!C3</f>
         <v>-41909.560000000005</v>
       </c>
       <c r="H9" s="12">
@@ -2022,15 +2043,15 @@
         <v>45</v>
       </c>
       <c r="E10" s="9">
-        <f>+[12]Main!$J$2</f>
+        <f>+[6]Main!$J$2</f>
         <v>87.92</v>
       </c>
       <c r="F10" s="12">
-        <f>+([12]Main!$J$4)*FX!C2</f>
+        <f>+([6]Main!$J$4)*FX!C2</f>
         <v>6994.2646728863992</v>
       </c>
       <c r="G10" s="12">
-        <f>+([12]Main!$J$6-[12]Main!$J$5)*FX!C2</f>
+        <f>+([6]Main!$J$6-[6]Main!$J$5)*FX!C2</f>
         <v>256.17617999999993</v>
       </c>
       <c r="H10" s="12">
@@ -2078,15 +2099,15 @@
         <v>51</v>
       </c>
       <c r="E11" s="9">
-        <f>+[13]Main!$I$2</f>
+        <f>+[7]Main!$I$2</f>
         <v>160.9</v>
       </c>
       <c r="F11" s="12">
-        <f>+[13]Main!$I$4*FX!C3</f>
+        <f>+[7]Main!$I$4*FX!C3</f>
         <v>29939.216496000005</v>
       </c>
       <c r="G11" s="12">
-        <f>+([13]Main!$I$6-[13]Main!$I$5)*FX!C3</f>
+        <f>+([7]Main!$I$6-[7]Main!$I$5)*FX!C3</f>
         <v>-1927.1995400000001</v>
       </c>
       <c r="H11" s="12">
@@ -2134,15 +2155,15 @@
         <v>24</v>
       </c>
       <c r="E12" s="9">
-        <f>+[14]Main!$H$2</f>
+        <f>+[8]Main!$H$2</f>
         <v>113.5</v>
       </c>
       <c r="F12" s="12">
-        <f>+[14]Main!$H$4</f>
+        <f>+[8]Main!$H$4</f>
         <v>50394</v>
       </c>
       <c r="G12" s="12">
-        <f>+([14]Main!$H$6-[14]Main!$H$5)</f>
+        <f>+([8]Main!$H$6-[8]Main!$H$5)</f>
         <v>3827</v>
       </c>
       <c r="H12" s="12">
@@ -2187,15 +2208,15 @@
         <v>24</v>
       </c>
       <c r="E13" s="9">
-        <f>+[15]Main!$I$2</f>
+        <f>+[9]Main!$I$2</f>
         <v>50.7</v>
       </c>
       <c r="F13" s="12">
-        <f>+[15]Main!$I$4</f>
+        <f>+[9]Main!$I$4</f>
         <v>27269.090670900005</v>
       </c>
       <c r="G13" s="12">
-        <f>+[15]Main!$I$6-[15]Main!$I$5</f>
+        <f>+[9]Main!$I$6-[9]Main!$I$5</f>
         <v>29131</v>
       </c>
       <c r="H13" s="12">
@@ -2265,7 +2286,7 @@
       <c r="I15" s="8"/>
       <c r="M15" s="19">
         <f>+AVERAGE(M5:M13)</f>
-        <v>-0.12015001731183217</v>
+        <v>-0.12642896854213692</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -2957,15 +2978,15 @@
         <v>78</v>
       </c>
       <c r="E5" s="9">
-        <f>+[1]Main!$H$3</f>
+        <f>+[10]Main!$H$3</f>
         <v>47.45</v>
       </c>
       <c r="F5" s="12">
-        <f>+[1]Main!$H$5*FX!C11</f>
+        <f>+[10]Main!$H$5*FX!C11</f>
         <v>121803.201</v>
       </c>
       <c r="G5" s="12">
-        <f>+([1]Main!$H$7-[1]Main!$H$6)*FX!C11</f>
+        <f>+([10]Main!$H$7-[10]Main!$H$6)*FX!C11</f>
         <v>38077.649999999994</v>
       </c>
       <c r="H5" s="12">
@@ -2993,7 +3014,7 @@
         <v>0.70740671257354304</v>
       </c>
       <c r="O5" s="33">
-        <f>+[1]DCF!$J$4</f>
+        <f>+[10]DCF!$J$4</f>
         <v>55.220363038811023</v>
       </c>
       <c r="P5" s="34">
@@ -3019,15 +3040,15 @@
         <v>77</v>
       </c>
       <c r="E6" s="9">
-        <f>+[2]Main!$I$2</f>
+        <f>+[11]Main!$I$2</f>
         <v>58.7</v>
       </c>
       <c r="F6" s="12">
-        <f>+[2]Main!$I$4*FX!C12</f>
+        <f>+[11]Main!$I$4*FX!C12</f>
         <v>45818.872000000003</v>
       </c>
       <c r="G6" s="12">
-        <f>+([2]Main!$I$6-[2]Main!$I$5)*FX!C12</f>
+        <f>+([11]Main!$I$6-[11]Main!$I$5)*FX!C12</f>
         <v>1886.72</v>
       </c>
       <c r="H6" s="12">
@@ -3055,7 +3076,7 @@
         <v>-4.2476481764678442E-2</v>
       </c>
       <c r="O6" s="33">
-        <f>+[2]DCF!$J$4</f>
+        <f>+[11]DCF!$J$4</f>
         <v>90.720141570568231</v>
       </c>
       <c r="P6" s="34">
@@ -3081,15 +3102,15 @@
         <v>75</v>
       </c>
       <c r="E7" s="9">
-        <f>+[3]Main!$J$2</f>
+        <f>+[12]Main!$J$2</f>
         <v>71.599999999999994</v>
       </c>
       <c r="F7" s="12">
-        <f>+[3]Main!$J$4*FX!C13</f>
+        <f>+[12]Main!$J$4*FX!C13</f>
         <v>731.79496000000006</v>
       </c>
       <c r="G7" s="12">
-        <f>+([3]Main!$J$6-[3]Main!$J$5)*FX!C13</f>
+        <f>+([12]Main!$J$6-[12]Main!$J$5)*FX!C13</f>
         <v>634.43899999999996</v>
       </c>
       <c r="H7" s="12">
@@ -3117,7 +3138,7 @@
         <v>-0.2174863387978142</v>
       </c>
       <c r="O7" s="33">
-        <f>+[3]DCF!$J$4</f>
+        <f>+[12]DCF!$J$4</f>
         <v>108.99870635334247</v>
       </c>
       <c r="P7" s="34">
@@ -3143,15 +3164,15 @@
         <v>16</v>
       </c>
       <c r="E8" s="9">
-        <f>+[4]Main!$I$3</f>
+        <f>+[13]Main!$I$3</f>
         <v>38.979999999999997</v>
       </c>
       <c r="F8" s="12">
-        <f>+[4]Main!$I$5</f>
+        <f>+[13]Main!$I$5</f>
         <v>11937.624999999998</v>
       </c>
       <c r="G8" s="12">
-        <f>+[4]Main!$I$7-[4]Main!$I$6</f>
+        <f>+[13]Main!$I$7-[13]Main!$I$6</f>
         <v>5880</v>
       </c>
       <c r="H8" s="12">
@@ -3171,7 +3192,7 @@
         <v>56.9</v>
       </c>
       <c r="M8" s="9">
-        <f>+[4]Main!$I$3</f>
+        <f>+[13]Main!$I$3</f>
         <v>38.979999999999997</v>
       </c>
       <c r="N8" s="18">
@@ -3203,15 +3224,15 @@
         <v>16</v>
       </c>
       <c r="E9" s="9">
-        <f>+[5]Main!$H$2</f>
+        <f>+[14]Main!$H$2</f>
         <v>101.5</v>
       </c>
       <c r="F9" s="12">
-        <f>+[5]Main!$H$4</f>
+        <f>+[14]Main!$H$4</f>
         <v>691.47869700000001</v>
       </c>
       <c r="G9" s="12">
-        <f>+[5]Main!$H$6</f>
+        <f>+[14]Main!$H$6</f>
         <v>15.463999999999999</v>
       </c>
       <c r="H9" s="12">
@@ -3231,7 +3252,7 @@
         <v>74.495000000000005</v>
       </c>
       <c r="M9" s="9">
-        <f>+[5]Main!$H$2</f>
+        <f>+[14]Main!$H$2</f>
         <v>101.5</v>
       </c>
       <c r="N9" s="18">
@@ -3239,7 +3260,7 @@
         <v>0.36250755084233832</v>
       </c>
       <c r="O9" s="33">
-        <f>+[5]DCF!$J$3</f>
+        <f>+[14]DCF!$J$3</f>
         <v>97.40723155701005</v>
       </c>
       <c r="P9" s="34">
@@ -3266,15 +3287,15 @@
         <v>71</v>
       </c>
       <c r="E10" s="9">
-        <f>+[6]Main!$H$2</f>
+        <f>+[15]Main!$H$2</f>
         <v>250.5</v>
       </c>
       <c r="F10" s="12">
-        <f>+[6]Main!$H$4</f>
+        <f>+[15]Main!$H$4</f>
         <v>30716.233848</v>
       </c>
       <c r="G10" s="12">
-        <f>+[6]Main!$H$6-[6]Main!$H$5</f>
+        <f>+[15]Main!$H$6-[15]Main!$H$5</f>
         <v>3324</v>
       </c>
       <c r="H10" s="12">
@@ -3294,7 +3315,7 @@
         <v>226.89</v>
       </c>
       <c r="M10" s="9">
-        <f>+[6]Main!$H$2</f>
+        <f>+[15]Main!$H$2</f>
         <v>250.5</v>
       </c>
       <c r="N10" s="18">
@@ -3302,7 +3323,7 @@
         <v>0.10405923575300813</v>
       </c>
       <c r="O10" s="9">
-        <f>+[6]DCF!$J$4</f>
+        <f>+[15]DCF!$J$4</f>
         <v>379.40823731776692</v>
       </c>
       <c r="P10" s="34">
@@ -3329,20 +3350,20 @@
         <v>77</v>
       </c>
       <c r="E11" s="9">
-        <f>+[7]Main!$I$2</f>
-        <v>110.86</v>
+        <f>+[3]Main!$I$2</f>
+        <v>99.65</v>
       </c>
       <c r="F11" s="12">
-        <f>+[7]Main!$I$4</f>
-        <v>12021.43191302</v>
+        <f>+[3]Main!$I$4</f>
+        <v>10522.448477600001</v>
       </c>
       <c r="G11" s="12">
-        <f>+[7]Main!$I$6-[7]Main!$I$5</f>
-        <v>-1514.729</v>
+        <f>+[3]Main!$I$6-[3]Main!$I$5</f>
+        <v>-189.73699999999999</v>
       </c>
       <c r="H11" s="12">
         <f t="shared" si="0"/>
-        <v>10506.702913020001</v>
+        <v>10332.711477600002</v>
       </c>
       <c r="I11" s="46" t="s">
         <v>40</v>
@@ -3405,6 +3426,128 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3F6DB27-CD5A-41FF-9240-6089D583EE97}">
+  <dimension ref="A1:P13"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="4.28515625" style="50" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" style="50" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="50"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16">
+      <c r="A1" s="49" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" s="50" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" s="51">
+        <v>1</v>
+      </c>
+      <c r="B5" s="49" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" s="51">
+        <f>+A5+1</f>
+        <v>2</v>
+      </c>
+      <c r="B6" s="49" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" s="51">
+        <f t="shared" ref="A7:A13" si="0">+A6+1</f>
+        <v>3</v>
+      </c>
+      <c r="B7" s="49"/>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" s="51">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B8" s="49"/>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9" s="51">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B9" s="49"/>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10" s="51">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B10" s="49"/>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11" s="51">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B11" s="49"/>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12" s="51">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B12" s="49"/>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13" s="51">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B13" s="49"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{ABB076BB-D49B-4B36-ABE5-C8895F16E268}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03B2DF4B-01E2-41F7-B53D-8680A3262A00}">
   <dimension ref="A1:CB334"/>
   <sheetFormatPr defaultRowHeight="15"/>
